--- a/results/Network_Topology_03/results_request_20.xlsx
+++ b/results/Network_Topology_03/results_request_20.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,47 +466,1174 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7.9</v>
+        <v>12.47</v>
       </c>
       <c r="C2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G11" t="n">
         <v>2.74</v>
       </c>
-      <c r="D2" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="E2" t="n">
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="C14" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D15" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8.56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="D20" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="C22" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="D23" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="D25" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G25" t="n">
         <v>2.34</v>
       </c>
-      <c r="F2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="C27" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="C28" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="C30" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="D30" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="C31" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="C32" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="C33" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="D33" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="D34" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="D35" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="D36" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="D40" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="C41" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="D41" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="E41" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="C43" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="D43" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="C44" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="D44" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="E44" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="E45" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="D46" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="C47" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="D47" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="C48" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="E48" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="D49" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="C51" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="D3" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.35</v>
+      <c r="B52" t="n">
+        <v>8.4278</v>
+      </c>
+      <c r="C52" t="n">
+        <v>5.515</v>
+      </c>
+      <c r="D52" t="n">
+        <v>8.646000000000001</v>
+      </c>
+      <c r="E52" t="n">
+        <v>5.1914</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.4694</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2.2612</v>
       </c>
     </row>
   </sheetData>
@@ -520,7 +1647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,28 +1706,1155 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
+      <c r="B52" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
